--- a/data/trans_dic/P44A$endoscopia-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44A$endoscopia-Edad-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -615,7 +615,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -625,47 +625,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>44,2%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>70,12%</t>
         </is>
       </c>
     </row>
@@ -678,54 +678,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,29; 92,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,65; 73,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,13; 95,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,53; 83,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>14,85; 76,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17,58; 33,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>46,87; 80,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,28; 69,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>22,24; 91,81</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -735,47 +735,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -788,54 +788,54 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,54; 77,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>38,47; 67,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,24; 48,83</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>44,43; 80,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>41,6; 75,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,31; 34,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>50,21; 74,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,41; 66,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>31,62; 40,2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -845,47 +845,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>73,52%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,97%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,31%</t>
         </is>
       </c>
     </row>
@@ -898,54 +898,54 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>55,2; 87,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26,83; 56,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39,32; 52,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43,44; 78,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>40,8; 75,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,53; 41,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>55,34; 79,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,47; 59,52</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36,78; 45,5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -955,47 +955,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>56,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>55,13%</t>
         </is>
       </c>
     </row>
@@ -1008,54 +1008,54 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>38,82; 90,42</t>
+          <t>23,93; 61,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>36,2; 75,31</t>
+          <t>46,53; 73,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21,27; 95,85</t>
+          <t>46,4; 62,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39,88; 79,13</t>
+          <t>31,14; 74,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 75,05</t>
+          <t>34,4; 74,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,07; 33,72</t>
+          <t>48,37; 61,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,84; 78,96</t>
+          <t>32,47; 61,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>35,66; 68,35</t>
+          <t>44,74; 69,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,1; 94,06</t>
+          <t>50,23; 60,86</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1065,47 +1065,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63,94%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>56,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>51,38%</t>
         </is>
       </c>
     </row>
@@ -1118,389 +1118,59 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>42,98; 77,81</t>
+          <t>52,35; 71,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,6; 67,47</t>
+          <t>43,79; 60,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34,59; 48,17</t>
+          <t>41,8; 82,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44,82; 82,47</t>
+          <t>51,64; 71,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>41,28; 74,55</t>
+          <t>45,02; 65,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,96; 34,44</t>
+          <t>33,29; 39,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,58; 74,6</t>
+          <t>54,51; 68,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>45,33; 66,8</t>
+          <t>47,59; 59,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31,08; 40,27</t>
+          <t>38,93; 74,85</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>73,52%</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>40,71%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>45,97%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>62,68%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>58,67%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>35,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>48,17%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>41,31%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n"/>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>55,16; 87,4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>26,79; 56,78</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>39,97; 52,02</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>44,23; 79,24</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>39,75; 76,48</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>30,5; 41,71</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>55,35; 80,08</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>36,48; 60,29</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>37,08; 45,58</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>41,01%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>60,29%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>54,92%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>56,83%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>55,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>48,25%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>57,73%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>55,13%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>24,33; 62,02</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>42,67; 74,37</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>46,2; 62,91</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30,91; 78,23</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>36,06; 73,15</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>48,45; 62,15</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>32,05; 62,38</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>45,67; 70,34</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>49,79; 60,47</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>61,34%</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>51,79%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>60,57%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>61,83%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>56,09%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>36,46%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>61,59%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>53,6%</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>51,38%</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n"/>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>51,6; 71,36</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>44,01; 59,97</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>41,3; 83,32</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>51,77; 71,17</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>45,85; 65,62</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>33,06; 39,47</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>54,6; 69,23</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>47,22; 59,71</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>38,95; 72,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
@@ -1508,11 +1178,8 @@
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1524,7 +1191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1543,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon</t>
+          <t>Población a la que le han realizado al menos una endoscopia para detectar cáncer de colon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1634,7 +1301,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>16-24</t>
+          <t>45-54</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1644,47 +1311,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56</t>
         </is>
       </c>
     </row>
@@ -1697,47 +1364,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9738</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>14918</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>265903</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4879</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19797</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>283751</t>
         </is>
       </c>
     </row>
@@ -1750,54 +1417,54 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>5568; 13141</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9547; 19618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>73724; 317149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>8313; 17165</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1639; 8406</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12564; 24088</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16254; 27904</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13342; 26276</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>89979; 371501</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>25-34</t>
+          <t>55-64</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1807,47 +1474,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>165</t>
         </is>
       </c>
     </row>
@@ -1860,47 +1527,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>24494</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>27843</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>76236</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21590</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22080</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>45366</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>46084</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>49923</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>121602</t>
         </is>
       </c>
     </row>
@@ -1913,54 +1580,54 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>17130; 30589</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>20158; 35144</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64582; 89489</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15002; 27077</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>15742; 28496</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>37876; 54064</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>36707; 54470</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>39169; 59823</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>107199; 136280</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>35-44</t>
+          <t>65-74</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1970,47 +1637,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>106</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>221</t>
         </is>
       </c>
     </row>
@@ -2023,47 +1690,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22507</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>17877</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>75311</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>19672</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>18301</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>51471</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>126782</t>
         </is>
       </c>
     </row>
@@ -2076,54 +1743,54 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>16900; 26852</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>11782; 24797</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>64426; 85220</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>13632; 24577</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12727; 23553</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>43670; 59996</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34312; 49518</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>26639; 44699</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>112863; 139625</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>45-54</t>
+          <t>75 o más</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2133,47 +1800,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>118</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>202</t>
         </is>
       </c>
     </row>
@@ -2186,47 +1853,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9738</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>22065</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>265903</t>
+          <t>52979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12764</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>19880</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>59618</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>22454</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>19797</t>
+          <t>41946</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>283751</t>
+          <t>112598</t>
         </is>
       </c>
     </row>
@@ -2239,54 +1906,54 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5502; 12814</t>
+          <t>6039; 15613</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9695; 20169</t>
+          <t>17030; 27069</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70873; 319346</t>
+          <t>44760; 59810</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8180; 16228</t>
+          <t>6632; 15831</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1227; 8283</t>
+          <t>12404; 26830</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12203; 24106</t>
+          <t>52134; 66690</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15899; 27386</t>
+          <t>15111; 28745</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13487; 25849</t>
+          <t>32505; 50263</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>93463; 380599</t>
+          <t>102595; 124308</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>55-64</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -2296,47 +1963,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>312</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>61</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>55</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>332</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>118</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>136</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>644</t>
         </is>
       </c>
     </row>
@@ -2349,47 +2016,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24494</t>
+          <t>67090</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>27843</t>
+          <t>82704</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76236</t>
+          <t>470429</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21590</t>
+          <t>66129</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22080</t>
+          <t>65140</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>174304</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46084</t>
+          <t>133220</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49923</t>
+          <t>147844</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>121602</t>
+          <t>644732</t>
         </is>
       </c>
     </row>
@@ -2402,559 +2069,67 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16910; 30611</t>
+          <t>57249; 77847</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>20226; 35352</t>
+          <t>69928; 95964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63377; 88276</t>
+          <t>324645; 638546</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15133; 27844</t>
+          <t>55232; 76516</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15619; 28211</t>
+          <t>52283; 76630</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37333; 53653</t>
+          <t>159143; 189444</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36980; 54535</t>
+          <t>117916; 147087</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>40907; 60281</t>
+          <t>131253; 165398</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>105389; 136532</t>
+          <t>488561; 939193</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>65-74</t>
-        </is>
-      </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>22507</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>17877</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>75311</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>19672</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>18301</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>51471</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>42179</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>36178</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>126782</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n"/>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>16888; 26756</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>11763; 24932</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>65488; 85232</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>13880; 24868</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>12400; 23856</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>43627; 59671</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>34318; 49646</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>27397; 45277</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>113810; 139881</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>75 o más</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>10352</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>22065</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>52979</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>12102</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>19880</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>59618</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>22454</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>41946</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>112598</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>6141; 15655</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>15616; 27216</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>44571; 60691</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>6583; 16659</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>13001; 26375</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>52222; 66986</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>14915; 29028</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>33184; 51107</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>101702; 123504</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n"/>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>67090</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>82704</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>470429</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>66129</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>65140</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>174304</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>133220</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>147844</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>644732</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>56432; 78039</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>70282; 95764</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>320782; 647154</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>55368; 76114</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>53248; 76196</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>158068; 188697</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>118116; 149759</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>130232; 164680</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>488756; 910962</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="9">
     <mergeCell ref="C1:E1"/>
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
-    <mergeCell ref="A25:A27"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P44A$endoscopia-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P44A$endoscopia-Edad-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>26,86%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>39,29; 92,73</t>
+          <t>40,36; 92,15</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35,65; 73,25</t>
+          <t>36,78; 76,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22,13; 95,19</t>
+          <t>19,0; 37,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>40,53; 83,7</t>
+          <t>40,56; 83,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,85; 76,16</t>
+          <t>14,97; 81,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,58; 33,7</t>
+          <t>18,06; 34,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,87; 80,46</t>
+          <t>47,56; 80,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,28; 69,48</t>
+          <t>33,85; 67,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,24; 91,81</t>
+          <t>20,78; 33,69</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41,6%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>43,54; 77,75</t>
+          <t>43,68; 77,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>38,47; 67,07</t>
+          <t>38,99; 66,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35,24; 48,83</t>
+          <t>34,53; 48,07</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,43; 80,19</t>
+          <t>43,86; 79,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>41,6; 75,31</t>
+          <t>42,26; 75,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,31; 34,7</t>
+          <t>23,19; 34,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,21; 74,51</t>
+          <t>51,11; 75,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,41; 66,3</t>
+          <t>44,64; 66,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>31,62; 40,2</t>
+          <t>31,13; 39,91</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,51%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55,2; 87,71</t>
+          <t>54,12; 88,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26,83; 56,47</t>
+          <t>27,49; 59,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,32; 52,02</t>
+          <t>40,2; 52,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43,44; 78,31</t>
+          <t>45,58; 80,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40,8; 75,51</t>
+          <t>40,95; 76,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>30,53; 41,94</t>
+          <t>30,6; 41,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>55,34; 79,87</t>
+          <t>54,56; 79,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,47; 59,52</t>
+          <t>36,85; 60,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>36,78; 45,5</t>
+          <t>37,23; 45,9</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>55,13%</t>
+          <t>55,24%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>23,93; 61,86</t>
+          <t>24,02; 62,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>46,53; 73,96</t>
+          <t>44,04; 74,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46,4; 62,0</t>
+          <t>47,77; 62,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31,14; 74,34</t>
+          <t>33,33; 78,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,4; 74,41</t>
+          <t>33,23; 72,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>48,37; 61,88</t>
+          <t>48,26; 61,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>32,47; 61,77</t>
+          <t>32,4; 62,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>44,74; 69,18</t>
+          <t>44,42; 69,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>50,23; 60,86</t>
+          <t>50,06; 60,58</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>39,99%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>52,35; 71,18</t>
+          <t>50,73; 71,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43,79; 60,1</t>
+          <t>43,78; 59,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41,8; 82,21</t>
+          <t>39,24; 47,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51,64; 71,54</t>
+          <t>51,54; 71,3</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,02; 65,99</t>
+          <t>45,67; 65,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,29; 39,62</t>
+          <t>33,4; 39,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,51; 68,0</t>
+          <t>54,16; 68,36</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>47,59; 59,97</t>
+          <t>47,5; 60,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,93; 74,85</t>
+          <t>37,66; 42,33</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>265903</t>
+          <t>26533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17848</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>283751</t>
+          <t>46137</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5568; 13141</t>
+          <t>5719; 13060</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9547; 19618</t>
+          <t>9849; 20432</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73724; 317149</t>
+          <t>18054; 35414</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8313; 17165</t>
+          <t>8319; 17101</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1639; 8406</t>
+          <t>1653; 9036</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12564; 24088</t>
+          <t>13864; 26262</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16254; 27904</t>
+          <t>16494; 28066</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13342; 26276</t>
+          <t>12800; 25632</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>89979; 371501</t>
+          <t>35695; 57854</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>76236</t>
+          <t>80660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45366</t>
+          <t>49882</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>121602</t>
+          <t>130542</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17130; 30589</t>
+          <t>17183; 30448</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20158; 35144</t>
+          <t>20430; 34600</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64582; 89489</t>
+          <t>66843; 93045</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15002; 27077</t>
+          <t>14810; 26899</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15742; 28496</t>
+          <t>15991; 28601</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37876; 54064</t>
+          <t>40477; 60265</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36707; 54470</t>
+          <t>37366; 55364</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39169; 59823</t>
+          <t>40279; 59663</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>107199; 136280</t>
+          <t>114589; 146924</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75311</t>
+          <t>82329</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>51471</t>
+          <t>56780</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>126782</t>
+          <t>139110</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16900; 26852</t>
+          <t>16567; 27126</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>11782; 24797</t>
+          <t>12070; 26007</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64426; 85220</t>
+          <t>71397; 94040</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13632; 24577</t>
+          <t>14305; 25237</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12727; 23553</t>
+          <t>12774; 23829</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43670; 59996</t>
+          <t>48218; 65751</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>34312; 49518</t>
+          <t>33825; 49214</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26639; 44699</t>
+          <t>27676; 45301</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>112863; 139625</t>
+          <t>124768; 153826</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>52979</t>
+          <t>57882</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1878,7 +1878,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59618</t>
+          <t>65917</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>112598</t>
+          <t>123799</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6039; 15613</t>
+          <t>6062; 15706</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17030; 27069</t>
+          <t>16117; 27433</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44760; 59810</t>
+          <t>50013; 65553</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6632; 15831</t>
+          <t>7098; 16636</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12404; 26830</t>
+          <t>11980; 26183</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52134; 66690</t>
+          <t>57623; 73695</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>15111; 28745</t>
+          <t>15077; 28996</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32505; 50263</t>
+          <t>32274; 50415</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102595; 124308</t>
+          <t>112182; 135760</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>470429</t>
+          <t>247403</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>174304</t>
+          <t>192185</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>644732</t>
+          <t>439588</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>57249; 77847</t>
+          <t>55486; 78290</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>69928; 95964</t>
+          <t>69918; 94738</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>324645; 638546</t>
+          <t>224008; 268391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>55232; 76516</t>
+          <t>55119; 76255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>52283; 76630</t>
+          <t>53034; 75580</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>159143; 189444</t>
+          <t>176466; 209550</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>117916; 147087</t>
+          <t>117157; 147876</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>131253; 165398</t>
+          <t>131008; 166096</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>488561; 939193</t>
+          <t>413953; 465238</t>
         </is>
       </c>
     </row>
